--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484144_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484144_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>A. SENGHOR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5808</v>
+        <v>4.4786</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3739</v>
+        <v>3.6261</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2069</v>
+        <v>0.8525</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.1143</v>
+        <v>2.7079</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.1429</v>
+        <v>1.3761</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0286</v>
+        <v>1.3318</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1219</v>
+        <v>3.2916</v>
       </c>
       <c r="K2" t="n">
-        <v>0.521</v>
+        <v>1.9663</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.3991</v>
+        <v>1.3253</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2362</v>
+        <v>-0.5837</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6638</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4276</v>
+        <v>0.0065</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7774</v>
+        <v>2.3806</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.7693</v>
+        <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2796</v>
+        <v>0.5966</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2278</v>
+        <v>0.3345</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0519</v>
+        <v>0.2621</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3619</v>
+        <v>-1.2065</v>
       </c>
       <c r="W2" t="n">
-        <v>3.0162</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.3781</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SENGHOR</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.072</v>
+        <v>3.319</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3597</v>
+        <v>3.3366</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7123</v>
+        <v>-0.0176</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7079</v>
+        <v>-1.1143</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3761</v>
+        <v>-1.1429</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3318</v>
+        <v>0.0286</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2916</v>
+        <v>0.1219</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9663</v>
+        <v>0.521</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3253</v>
+        <v>-0.3991</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5837</v>
+        <v>-1.2362</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-1.6638</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0065</v>
+        <v>0.4276</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3806</v>
+        <v>2.7774</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>3.7693</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1899</v>
+        <v>2.0179</v>
       </c>
       <c r="T3" t="n">
-        <v>0.06809999999999999</v>
+        <v>1.1905</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1218</v>
+        <v>0.8274</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2065</v>
+        <v>-0.3619</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.0162</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2065</v>
+        <v>-3.3781</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3514</v>
+        <v>2.8603</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3589</v>
+        <v>0.9283</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9925</v>
+        <v>1.932</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3706</v>
+        <v>3.205</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4625</v>
+        <v>2.4239</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9082</v>
+        <v>0.7812</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.1425</v>
+        <v>4.2397</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0573</v>
+        <v>3.7501</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1997</v>
+        <v>0.4896</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2281</v>
+        <v>-1.0346</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-1.3262</v>
       </c>
       <c r="O4" t="n">
         <v>0.2916</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9838</v>
+        <v>-3.9677</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9758</v>
+        <v>2.7774</v>
       </c>
       <c r="S4" t="n">
-        <v>2.8143</v>
+        <v>0.2423</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2788</v>
+        <v>-0.1416</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5355</v>
+        <v>0.3839</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.6032</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2065</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2907</v>
+        <v>-0.1947</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BLÁZQUEZ FARRIOL</t>
+          <t>J. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0252</v>
+        <v>2.1563</v>
       </c>
       <c r="E5" t="n">
-        <v>0.546</v>
+        <v>1.2466</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4793</v>
+        <v>0.9096</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0403</v>
+        <v>2.181</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5998</v>
+        <v>2.1318</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.64</v>
+        <v>0.0492</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.327</v>
+        <v>2.3008</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9932</v>
+        <v>2.2581</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3202</v>
+        <v>0.0427</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2867</v>
+        <v>-0.1198</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3935</v>
+        <v>-0.1263</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6802</v>
+        <v>0.0065</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>2.579</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6768</v>
+        <v>0.897</v>
       </c>
       <c r="T5" t="n">
-        <v>0.873</v>
+        <v>0.6122</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1961</v>
+        <v>0.2848</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2.5089</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.8344</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>A. BLÁZQUEZ FARRIOL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0199</v>
+        <v>1.9266</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0523</v>
+        <v>0.2229</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0722</v>
+        <v>1.7037</v>
       </c>
       <c r="G6" t="n">
-        <v>3.205</v>
+        <v>-0.0403</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4239</v>
+        <v>0.5998</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7812</v>
+        <v>-0.64</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2397</v>
+        <v>-0.327</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7501</v>
+        <v>0.9932</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4896</v>
+        <v>-1.3202</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0346</v>
+        <v>0.2867</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3262</v>
+        <v>-0.3935</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2916</v>
+        <v>0.6802</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7774</v>
+        <v>1.3887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.598</v>
+        <v>0.5782</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1222</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5242</v>
+        <v>0.0283</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CAMPENY LLOVERAS</t>
+          <t>T. KOHAN LÓPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8414</v>
+        <v>1.9086</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1843</v>
+        <v>1.5684</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6571</v>
+        <v>0.3402</v>
       </c>
       <c r="G7" t="n">
-        <v>2.181</v>
+        <v>1.0859</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1318</v>
+        <v>0.0703</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0492</v>
+        <v>1.0156</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3008</v>
+        <v>1.6761</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2581</v>
+        <v>1.0686</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0427</v>
+        <v>0.6075</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1198</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1263</v>
+        <v>-0.9983</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0065</v>
+        <v>0.4081</v>
       </c>
       <c r="P7" t="n">
         <v>1.5871</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.579</v>
+        <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5822000000000001</v>
+        <v>-0.4024</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5499000000000001</v>
+        <v>-0.1077</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0323</v>
+        <v>-0.2948</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.5089</v>
+        <v>-0.3619</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8344</v>
+        <v>-0.3619</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.712</v>
+        <v>1.8404</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3004</v>
+        <v>0.1927</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0124</v>
+        <v>1.6477</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3319</v>
@@ -1078,13 +1078,13 @@
         <v>2.7774</v>
       </c>
       <c r="S8" t="n">
-        <v>1.905</v>
+        <v>2.0334</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5613</v>
+        <v>1.0544</v>
       </c>
       <c r="U8" t="n">
-        <v>1.3438</v>
+        <v>0.9791</v>
       </c>
       <c r="V8" t="n">
         <v>0.3373</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. KOHAN LÓPEZ</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.53</v>
+        <v>1.7328</v>
       </c>
       <c r="E9" t="n">
-        <v>1.302</v>
+        <v>-1.3057</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2279</v>
+        <v>3.0385</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0859</v>
+        <v>-0.4602</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0703</v>
+        <v>1.0427</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0156</v>
+        <v>-1.5029</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6761</v>
+        <v>0.5023</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0686</v>
+        <v>1.8952</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6075</v>
+        <v>-1.3929</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.9625</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9983</v>
+        <v>-0.8525</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4081</v>
+        <v>-0.11</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5871</v>
+        <v>3.7693</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7811</v>
+        <v>0.7695</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3741</v>
+        <v>0.1758</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.407</v>
+        <v>0.5936</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3619</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. ROSET CLAVERO</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1886</v>
+        <v>1.7033</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.331</v>
+        <v>-1.1489</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5196</v>
+        <v>2.8522</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1313</v>
+        <v>-1.3706</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2167</v>
+        <v>-0.4625</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9147</v>
+        <v>-0.9082</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7232</v>
+        <v>-1.1425</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0806</v>
+        <v>0.0573</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6425999999999999</v>
+        <v>-1.1997</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4081</v>
+        <v>-0.2281</v>
       </c>
       <c r="N10" t="n">
-        <v>0.136</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2721</v>
+        <v>0.2916</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9919</v>
+        <v>2.9758</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0572</v>
+        <v>1.1662</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0623</v>
+        <v>0.771</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1196</v>
+        <v>0.3953</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2907</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. LOPEZ SAURA</t>
+          <t>J. ROSET CLAVERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0486</v>
+        <v>1.4105</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0422</v>
+        <v>-0.0249</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0065</v>
+        <v>1.4354</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3831</v>
+        <v>1.1313</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3831</v>
+        <v>0.2167</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.9147</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0202</v>
+        <v>0.7232</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0202</v>
+        <v>0.0806</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4032</v>
+        <v>0.4081</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4032</v>
+        <v>0.136</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.2721</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3968</v>
+        <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0623</v>
+        <v>0.2792</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0623</v>
+        <v>0.2437</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.0354</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>M. LOPEZ SAURA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1618</v>
+        <v>0.0137</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7794</v>
+        <v>0.0202</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6176</v>
+        <v>-0.0065</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4602</v>
+        <v>-0.3831</v>
       </c>
       <c r="H12" t="n">
-        <v>1.0427</v>
+        <v>-0.3831</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5029</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5023</v>
+        <v>0.0202</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8952</v>
+        <v>0.0202</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3929</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9625</v>
+        <v>-0.4032</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8525</v>
+        <v>-0.4032</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.7693</v>
+        <v>0.3968</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1251</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2979</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1728</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3619</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3619</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7198</v>
+        <v>-0.7121</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0763</v>
+        <v>-0.8722</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3565</v>
+        <v>0.1601</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3564</v>
@@ -1468,13 +1468,13 @@
         <v>0.3968</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2318</v>
+        <v>0.2395</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1247</v>
+        <v>0.0794</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3565</v>
+        <v>0.1601</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.3911</v>
+        <v>22.638</v>
       </c>
       <c r="E14" t="n">
-        <v>6.543200000000001</v>
+        <v>7.7901</v>
       </c>
       <c r="F14" t="n">
         <v>14.8478</v>
       </c>
       <c r="G14" t="n">
-        <v>6.254300000000001</v>
+        <v>6.254299999999999</v>
       </c>
       <c r="H14" t="n">
         <v>6.352</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.09749999999999986</v>
+        <v>-0.09749999999999964</v>
       </c>
       <c r="J14" t="n">
         <v>12.3542</v>
@@ -1546,13 +1546,13 @@
         <v>25.7901</v>
       </c>
       <c r="S14" t="n">
-        <v>7.170299999999999</v>
+        <v>8.417399999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.515400000000001</v>
+        <v>4.762099999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.6553</v>
+        <v>3.6552</v>
       </c>
       <c r="V14" t="n">
         <v>-2.9448</v>
@@ -1561,7 +1561,7 @@
         <v>5.5526</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.497400000000001</v>
+        <v>-8.497399999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.969</v>
+        <v>1.2786</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8841</v>
+        <v>2.1699</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9151</v>
+        <v>-0.8913</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7327</v>
@@ -1624,13 +1624,13 @@
         <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0272</v>
+        <v>-0.6632</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4989</v>
+        <v>-0.2153</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4717</v>
+        <v>-0.4479</v>
       </c>
       <c r="V15" t="n">
         <v>1.881</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. VICENTE ALONSO</t>
+          <t>M. SMITH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.0804</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.1459</v>
+        <v>0.1945</v>
       </c>
       <c r="F16" t="n">
-        <v>1.475</v>
+        <v>-0.2749</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8933</v>
+        <v>-2.2894</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0151</v>
+        <v>-1.9449</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8782</v>
+        <v>-0.3445</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0493</v>
+        <v>-0.0039</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8708</v>
+        <v>0.5157</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1785</v>
+        <v>-0.5195</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.156</v>
+        <v>-2.2855</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8557</v>
+        <v>-2.4605</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6997</v>
+        <v>0.175</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.1822</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.1661</v>
+        <v>-3.1741</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9838</v>
+        <v>2.3806</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2629</v>
+        <v>-1.2201</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2356</v>
+        <v>-0.8501</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0273</v>
+        <v>-0.37</v>
       </c>
       <c r="V16" t="n">
-        <v>1.881</v>
+        <v>4.2226</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>4.2226</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SMITH</t>
+          <t>A. VICENTE ALONSO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0113</v>
+        <v>-0.2525</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3156</v>
+        <v>-1.8398</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6957</v>
+        <v>1.5872</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2894</v>
+        <v>0.8933</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9449</v>
+        <v>0.0151</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3445</v>
+        <v>0.8782</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0039</v>
+        <v>2.0493</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5157</v>
+        <v>1.8708</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5195</v>
+        <v>0.1785</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.2855</v>
+        <v>-1.156</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.4605</v>
+        <v>-1.8557</v>
       </c>
       <c r="O17" t="n">
-        <v>0.175</v>
+        <v>0.6997</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7935</v>
+        <v>-2.1822</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1741</v>
+        <v>-4.1661</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3806</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1511</v>
+        <v>-0.8446</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3602</v>
+        <v>-0.9295</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7907999999999999</v>
+        <v>0.0849</v>
       </c>
       <c r="V17" t="n">
-        <v>4.2226</v>
+        <v>1.881</v>
       </c>
       <c r="W17" t="n">
-        <v>4.2226</v>
+        <v>1.2065</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. TAVARES DE BRITO</t>
+          <t>J. MARTINEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2658</v>
+        <v>-1.4255</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.026</v>
+        <v>-3.1264</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7602</v>
+        <v>1.7009</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1054</v>
+        <v>-0.9805</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.3107</v>
+        <v>-0.1617</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4161</v>
+        <v>-0.8188</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1287</v>
+        <v>-0.4738</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5942</v>
+        <v>0.7661</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7229</v>
+        <v>-1.2399</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0233</v>
+        <v>-0.5067</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7165</v>
+        <v>-0.9278</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6932</v>
+        <v>0.4211</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9919</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.1822</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2953</v>
+        <v>-0.0482</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5044</v>
+        <v>-0.4704</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7996</v>
+        <v>0.4222</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARTINEZ SANCHEZ</t>
+          <t>J. ROYO SANTOS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5734</v>
+        <v>-1.7927</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3304</v>
+        <v>-0.898</v>
       </c>
       <c r="F19" t="n">
-        <v>1.757</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9805</v>
+        <v>-0.4607</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1617</v>
+        <v>-0.3377</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8188</v>
+        <v>-0.123</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4738</v>
+        <v>0.9327</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7661</v>
+        <v>0.9327</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2399</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5067</v>
+        <v>-1.3934</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9278</v>
+        <v>-1.2704</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4211</v>
+        <v>-0.123</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3968</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1822</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1961</v>
+        <v>-0.3401</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6744</v>
+        <v>0.1531</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4783</v>
+        <v>-0.4932</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ROYO SANTOS</t>
+          <t>W. TAVARES DE BRITO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.245</v>
+        <v>-2.0386</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1021</v>
+        <v>-2.4341</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1429</v>
+        <v>0.3955</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4607</v>
+        <v>0.1054</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3377</v>
+        <v>-1.3107</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.123</v>
+        <v>1.4161</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9327</v>
+        <v>0.1287</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9327</v>
+        <v>-0.5942</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.7229</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3934</v>
+        <v>-0.0233</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2704</v>
+        <v>-0.7165</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.123</v>
+        <v>0.6932</v>
       </c>
       <c r="P20" t="n">
         <v>-0.9919</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9838</v>
+        <v>-2.1822</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7924</v>
+        <v>-0.4776</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.051</v>
+        <v>-0.9125</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.4349</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8513</v>
+        <v>-2.4831</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8118</v>
+        <v>-1.6078</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0395</v>
+        <v>-0.8754</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3355</v>
@@ -2092,13 +2092,13 @@
         <v>1.1903</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9449</v>
+        <v>-0.5768</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3514</v>
+        <v>-0.1473</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5935</v>
+        <v>-0.4295</v>
       </c>
       <c r="V21" t="n">
         <v>1.2065</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6305</v>
+        <v>-3.2904</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8524</v>
+        <v>-2.6484</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7781</v>
+        <v>-0.642</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1567</v>
@@ -2170,13 +2170,13 @@
         <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2753</v>
+        <v>-0.9352</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.289</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9863</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6032</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ ALEJANDRE</t>
+          <t>A. NUÑEZ NAVARRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7466</v>
+        <v>-5.0311</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2892</v>
+        <v>-1.759</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4575</v>
+        <v>-3.2721</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1384</v>
+        <v>-0.1592</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1558</v>
+        <v>-2.0261</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2942</v>
+        <v>1.8669</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5742</v>
+        <v>0.9508</v>
       </c>
       <c r="K23" t="n">
-        <v>0.746</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3202</v>
+        <v>1.8474</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5642</v>
+        <v>-1.11</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-1.1295</v>
       </c>
       <c r="O23" t="n">
-        <v>0.026</v>
+        <v>0.0195</v>
       </c>
       <c r="P23" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-1.9838</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-2.9758</v>
       </c>
       <c r="R23" t="n">
         <v>0.9919</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5226</v>
+        <v>-1.0585</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9353</v>
+        <v>-0.3174</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4127</v>
+        <v>-0.7412</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1469</v>
+        <v>-2.8215</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6745</v>
+        <v>-0.4085</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4724</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. NUÑEZ NAVARRO</t>
+          <t>S. RODRIGUEZ ALEJANDRE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.3653</v>
+        <v>-5.5952</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0651</v>
+        <v>-4.1054</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.3002</v>
+        <v>-1.4897</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.1592</v>
+        <v>-1.1384</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0261</v>
+        <v>0.1558</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8669</v>
+        <v>-1.2942</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9508</v>
+        <v>-0.5742</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8967000000000001</v>
+        <v>0.746</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8474</v>
+        <v>-1.3202</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.11</v>
+        <v>-0.5642</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1295</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0195</v>
+        <v>0.026</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R24" t="n">
         <v>0.9919</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3927</v>
+        <v>-0.3259</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.1191</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7692</v>
+        <v>-0.445</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.8215</v>
+        <v>-2.1469</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.4085</v>
+        <v>-0.6745</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4129</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="25">
@@ -2359,28 +2359,28 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-21.3911</v>
+        <v>-20.7109</v>
       </c>
       <c r="E25" t="n">
-        <v>-16.0544</v>
+        <v>-16.0545</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.3368</v>
+        <v>-4.656499999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-6.2544</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.351900000000001</v>
+        <v>-6.3519</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09759999999999991</v>
+        <v>0.09760000000000013</v>
       </c>
       <c r="J25" t="n">
         <v>6.0999</v>
       </c>
       <c r="K25" t="n">
-        <v>7.5902</v>
+        <v>7.590199999999999</v>
       </c>
       <c r="L25" t="n">
         <v>-1.4903</v>
@@ -2404,13 +2404,13 @@
         <v>14.8787</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.170300000000001</v>
+        <v>-6.490200000000001</v>
       </c>
       <c r="T25" t="n">
         <v>-3.6553</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.515</v>
+        <v>-2.8351</v>
       </c>
       <c r="V25" t="n">
         <v>2.945000000000001</v>
